--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818305</v>
+        <v>6818304</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818304</v>
+        <v>6818305</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6014,7 +6014,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6243,7 +6243,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6355,7 +6355,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6467,7 +6467,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6584,7 +6584,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6808,7 +6808,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7037,7 +7037,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7149,7 +7149,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7261,7 +7261,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7373,7 +7373,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7490,7 +7490,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7938,7 +7938,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8386,7 +8386,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9821,7 +9821,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11601,7 +11601,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11723,7 +11723,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11957,7 +11957,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12079,7 +12079,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12313,7 +12313,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16930,7 +16930,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818305</v>
+        <v>6818304</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818304</v>
+        <v>6818305</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137071277</v>
       </c>
       <c r="B103" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137071199</v>
       </c>
       <c r="B104" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>137070033</v>
       </c>
       <c r="B115" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>137070039</v>
       </c>
       <c r="B116" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>137070044</v>
       </c>
       <c r="B117" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>137070062</v>
       </c>
       <c r="B118" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>137070071</v>
       </c>
       <c r="B119" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>137070075</v>
       </c>
       <c r="B120" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>137071228</v>
       </c>
       <c r="B121" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>137071236</v>
       </c>
       <c r="B122" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>137071237</v>
       </c>
       <c r="B123" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>137071241</v>
       </c>
       <c r="B124" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>137071245</v>
       </c>
       <c r="B125" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>137071248</v>
       </c>
       <c r="B126" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>137071255</v>
       </c>
       <c r="B127" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>137071280</v>
       </c>
       <c r="B128" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137071284</v>
       </c>
       <c r="B129" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>137071295</v>
       </c>
       <c r="B130" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137070041</v>
       </c>
       <c r="B131" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>137071201</v>
       </c>
       <c r="B132" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>137071235</v>
       </c>
       <c r="B133" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>137071240</v>
       </c>
       <c r="B136" t="n">
-        <v>56572</v>
+        <v>56585</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>137071276</v>
       </c>
       <c r="B137" t="n">
-        <v>56572</v>
+        <v>56585</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818305</v>
+        <v>6818304</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>137071277</v>
       </c>
       <c r="B103" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137071199</v>
       </c>
       <c r="B104" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>137070033</v>
       </c>
       <c r="B115" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>137070039</v>
       </c>
       <c r="B116" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>137070044</v>
       </c>
       <c r="B117" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>137070062</v>
       </c>
       <c r="B118" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>137070071</v>
       </c>
       <c r="B119" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>137070075</v>
       </c>
       <c r="B120" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>137071228</v>
       </c>
       <c r="B121" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>137071236</v>
       </c>
       <c r="B122" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>137071237</v>
       </c>
       <c r="B123" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>137071241</v>
       </c>
       <c r="B124" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>137071245</v>
       </c>
       <c r="B125" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>137071248</v>
       </c>
       <c r="B126" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>137071255</v>
       </c>
       <c r="B127" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>137071280</v>
       </c>
       <c r="B128" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137071284</v>
       </c>
       <c r="B129" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>137071295</v>
       </c>
       <c r="B130" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137070041</v>
       </c>
       <c r="B131" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>137071201</v>
       </c>
       <c r="B132" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>137071235</v>
       </c>
       <c r="B133" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>137070040</v>
       </c>
       <c r="B134" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>137071233</v>
       </c>
       <c r="B135" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>137071240</v>
       </c>
       <c r="B136" t="n">
-        <v>56585</v>
+        <v>56587</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>137071276</v>
       </c>
       <c r="B137" t="n">
-        <v>56585</v>
+        <v>56587</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -4885,11 +4885,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -6040,11 +6036,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -6493,11 +6485,7 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -6834,11 +6822,7 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -12461,11 +12445,7 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -12578,11 +12558,7 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -13921,11 +13897,7 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14038,11 +14010,7 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14155,11 +14123,7 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14272,11 +14236,7 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14389,11 +14349,7 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14506,11 +14462,7 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14623,11 +14575,7 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14740,11 +14688,7 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14857,11 +14801,7 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -14974,11 +14914,7 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15091,11 +15027,7 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15208,11 +15140,7 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15325,11 +15253,7 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15442,11 +15366,7 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15559,11 +15479,7 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15676,11 +15592,7 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15793,11 +15705,7 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -15910,11 +15818,7 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -16029,11 +15933,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -16152,11 +16052,7 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -16269,11 +16165,7 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -16386,11 +16278,7 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
@@ -16503,11 +16391,7 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>137071277</v>
       </c>
       <c r="B103" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137071199</v>
       </c>
       <c r="B104" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>137070033</v>
       </c>
       <c r="B115" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>137070039</v>
       </c>
       <c r="B116" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>137070044</v>
       </c>
       <c r="B117" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>137070062</v>
       </c>
       <c r="B118" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>137070071</v>
       </c>
       <c r="B119" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>137070075</v>
       </c>
       <c r="B120" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>137071228</v>
       </c>
       <c r="B121" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>137071236</v>
       </c>
       <c r="B122" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>137071237</v>
       </c>
       <c r="B123" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>137071241</v>
       </c>
       <c r="B124" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>137071245</v>
       </c>
       <c r="B125" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>137071248</v>
       </c>
       <c r="B126" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>137071255</v>
       </c>
       <c r="B127" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>137071280</v>
       </c>
       <c r="B128" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>137071284</v>
       </c>
       <c r="B129" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>137071295</v>
       </c>
       <c r="B130" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137070041</v>
       </c>
       <c r="B131" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>137071201</v>
       </c>
       <c r="B132" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>137071235</v>
       </c>
       <c r="B133" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>137070040</v>
       </c>
       <c r="B134" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>137071233</v>
       </c>
       <c r="B135" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>137071240</v>
       </c>
       <c r="B136" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>137071276</v>
       </c>
       <c r="B137" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071273</v>
       </c>
       <c r="B12" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070028</v>
       </c>
       <c r="B30" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070030</v>
       </c>
       <c r="B31" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070036</v>
       </c>
       <c r="B32" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818304</v>
+        <v>6818305</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4244,7 +4244,7 @@
         <v>137070038</v>
       </c>
       <c r="B33" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070058</v>
       </c>
       <c r="B34" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070061</v>
       </c>
       <c r="B35" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070068</v>
       </c>
       <c r="B36" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137070069</v>
       </c>
       <c r="B37" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137070070</v>
       </c>
       <c r="B38" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070073</v>
       </c>
       <c r="B39" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137070076</v>
       </c>
       <c r="B40" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137071204</v>
       </c>
       <c r="B41" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137071205</v>
       </c>
       <c r="B42" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137071209</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137071218</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137071229</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137071247</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137071253</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137071257</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>137071258</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>137071259</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>137071262</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>137071265</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         <v>137071267</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>137071271</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>137071272</v>
       </c>
       <c r="B55" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>137071275</v>
       </c>
       <c r="B56" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>137071278</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>137071279</v>
       </c>
       <c r="B58" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>137071281</v>
       </c>
       <c r="B59" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>137071282</v>
       </c>
       <c r="B60" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>137071286</v>
       </c>
       <c r="B61" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>137071288</v>
       </c>
       <c r="B62" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>137071290</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>137071291</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>137071293</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>137071294</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071220</v>
       </c>
       <c r="B69" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071232</v>
       </c>
       <c r="B70" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>137071234</v>
       </c>
       <c r="B71" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>137071210</v>
       </c>
       <c r="B74" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070048</v>
       </c>
       <c r="B75" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070059</v>
       </c>
       <c r="B76" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137070064</v>
       </c>
       <c r="B77" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071239</v>
       </c>
       <c r="B78" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071249</v>
       </c>
       <c r="B79" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137071251</v>
       </c>
       <c r="B80" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070047</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070049</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070050</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070051</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070054</v>
       </c>
       <c r="B85" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070056</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070060</v>
       </c>
       <c r="B87" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137070065</v>
       </c>
       <c r="B88" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071213</v>
       </c>
       <c r="B89" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>137071219</v>
       </c>
       <c r="B90" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>137071224</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>137071225</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>137071230</v>
       </c>
       <c r="B93" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>137071231</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071250</v>
       </c>
       <c r="B95" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071252</v>
       </c>
       <c r="B96" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>137071256</v>
       </c>
       <c r="B97" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071264</v>
       </c>
       <c r="B98" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071266</v>
       </c>
       <c r="B99" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>137071268</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>137071261</v>
       </c>
       <c r="B102" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>137071277</v>
       </c>
       <c r="B103" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>137071199</v>
       </c>
       <c r="B104" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>137070033</v>
       </c>
       <c r="B115" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>137070039</v>
       </c>
       <c r="B116" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>137070044</v>
       </c>
       <c r="B117" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>137070062</v>
       </c>
       <c r="B118" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>137070071</v>
       </c>
       <c r="B119" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>137070075</v>
       </c>
       <c r="B120" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>137071228</v>
       </c>
       <c r="B121" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>137071236</v>
       </c>
       <c r="B122" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>137071237</v>
       </c>
       <c r="B123" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>137071241</v>
       </c>
       <c r="B124" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>137071245</v>
       </c>
       <c r="B125" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>137071248</v>
       </c>
       <c r="B126" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>137071255</v>
       </c>
       <c r="B127" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>137071280</v>
       </c>
       <c r="B128" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>137071284</v>
       </c>
       <c r="B129" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>137071295</v>
       </c>
       <c r="B130" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137070041</v>
       </c>
       <c r="B131" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>137071201</v>
       </c>
       <c r="B132" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>137071235</v>
       </c>
       <c r="B133" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>137071240</v>
       </c>
       <c r="B136" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>137071276</v>
       </c>
       <c r="B137" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070057</v>
       </c>
       <c r="B141" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070063</v>
       </c>
       <c r="B142" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137070066</v>
       </c>
       <c r="B143" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>137071200</v>
       </c>
       <c r="B144" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137070052</v>
       </c>
       <c r="B146" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071212</v>
       </c>
       <c r="B147" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>137071254</v>
       </c>
       <c r="B148" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -1945,7 +1945,7 @@
         <v>137071244</v>
       </c>
       <c r="B13" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137071289</v>
       </c>
       <c r="B14" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>137070046</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137071221</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>137071222</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>401434</v>
       </c>
       <c r="R32" t="n">
-        <v>6818305</v>
+        <v>6818304</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -16478,7 +16478,7 @@
         <v>137071287</v>
       </c>
       <c r="B138" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>137071263</v>
       </c>
       <c r="B139" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ148"/>
+  <dimension ref="A1:AZ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,32 +1820,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137071273</v>
+        <v>137071244</v>
       </c>
       <c r="B12" t="n">
-        <v>81485</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401318</v>
+        <v>401425</v>
       </c>
       <c r="R12" t="n">
-        <v>6817944</v>
+        <v>6818208</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1936,16 +1936,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071273</t>
+          <t>https://artportalen.se/Sighting/137071244</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137071244</v>
+        <v>137071289</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401425</v>
+        <v>401179</v>
       </c>
       <c r="R13" t="n">
-        <v>6818208</v>
+        <v>6818031</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2058,51 +2058,60 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071244</t>
+          <t>https://artportalen.se/Sighting/137071289</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137071289</v>
+        <v>137070046</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>93507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401179</v>
+        <v>401329</v>
       </c>
       <c r="R14" t="n">
-        <v>6818031</v>
+        <v>6818433</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2134,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2153,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,41 +2164,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071289</t>
+          <t>https://artportalen.se/Sighting/137070046</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137070046</v>
+        <v>137071221</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,29 +2213,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401329</v>
+        <v>401343</v>
       </c>
       <c r="R15" t="n">
-        <v>6818433</v>
+        <v>6818419</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2265,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2275,7 +2265,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,27 +2280,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070046</t>
+          <t>https://artportalen.se/Sighting/137071221</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137071221</v>
+        <v>137071222</v>
       </c>
       <c r="B16" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,13 +2332,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401343</v>
+        <v>401345</v>
       </c>
       <c r="R16" t="n">
-        <v>6818419</v>
+        <v>6818425</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2413,38 +2403,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071221</t>
+          <t>https://artportalen.se/Sighting/137071222</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137071222</v>
+        <v>131046822</v>
       </c>
       <c r="B17" t="n">
-        <v>93501</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,13 +2444,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401345</v>
+        <v>401699</v>
       </c>
       <c r="R17" t="n">
-        <v>6818425</v>
+        <v>6818070</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2484,22 +2474,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,24 +2504,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071222</t>
+          <t>https://artportalen.se/Sighting/131046822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131046822</v>
+        <v>131046823</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2566,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401699</v>
+        <v>401661</v>
       </c>
       <c r="R18" t="n">
-        <v>6818070</v>
+        <v>6818064</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,13 +2627,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046822</t>
+          <t>https://artportalen.se/Sighting/131046823</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131046823</v>
+        <v>131046824</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2678,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>401661</v>
+        <v>401653</v>
       </c>
       <c r="R19" t="n">
-        <v>6818064</v>
+        <v>6818054</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,13 +2739,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046823</t>
+          <t>https://artportalen.se/Sighting/131046824</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131046824</v>
+        <v>131046825</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2790,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401653</v>
+        <v>401650</v>
       </c>
       <c r="R20" t="n">
-        <v>6818054</v>
+        <v>6818017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,13 +2851,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046824</t>
+          <t>https://artportalen.se/Sighting/131046825</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131046825</v>
+        <v>131046826</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2902,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401650</v>
+        <v>401647</v>
       </c>
       <c r="R21" t="n">
-        <v>6818017</v>
+        <v>6817965</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,13 +2963,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046825</t>
+          <t>https://artportalen.se/Sighting/131046826</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131046826</v>
+        <v>131046827</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401647</v>
+        <v>401630</v>
       </c>
       <c r="R22" t="n">
-        <v>6817965</v>
+        <v>6817911</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,13 +3075,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046826</t>
+          <t>https://artportalen.se/Sighting/131046827</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131046827</v>
+        <v>131046828</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3126,10 +3116,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401630</v>
+        <v>401634</v>
       </c>
       <c r="R23" t="n">
-        <v>6817911</v>
+        <v>6817871</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3161,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,13 +3187,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046827</t>
+          <t>https://artportalen.se/Sighting/131046828</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131046828</v>
+        <v>131046829</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3238,10 +3228,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401634</v>
+        <v>401574</v>
       </c>
       <c r="R24" t="n">
-        <v>6817871</v>
+        <v>6817873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3273,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,13 +3299,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046828</t>
+          <t>https://artportalen.se/Sighting/131046829</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131046829</v>
+        <v>131046830</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3350,10 +3340,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401574</v>
+        <v>401538</v>
       </c>
       <c r="R25" t="n">
-        <v>6817873</v>
+        <v>6818009</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3385,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,13 +3411,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046829</t>
+          <t>https://artportalen.se/Sighting/131046830</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131046830</v>
+        <v>131046831</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3462,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401538</v>
+        <v>401378</v>
       </c>
       <c r="R26" t="n">
-        <v>6818009</v>
+        <v>6818089</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3497,7 +3487,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,7 +3497,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,13 +3523,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046830</t>
+          <t>https://artportalen.se/Sighting/131046831</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131046831</v>
+        <v>131046832</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3574,10 +3564,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401378</v>
+        <v>401350</v>
       </c>
       <c r="R27" t="n">
-        <v>6818089</v>
+        <v>6818162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3609,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,13 +3635,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046831</t>
+          <t>https://artportalen.se/Sighting/131046832</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131046832</v>
+        <v>131046833</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3686,10 +3676,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401350</v>
+        <v>401322</v>
       </c>
       <c r="R28" t="n">
-        <v>6818162</v>
+        <v>6818367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,7 +3711,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3721,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3757,16 +3747,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046832</t>
+          <t>https://artportalen.se/Sighting/131046833</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131046833</v>
+        <v>137070028</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3798,13 +3788,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>401322</v>
+        <v>401655</v>
       </c>
       <c r="R29" t="n">
-        <v>6818367</v>
+        <v>6818195</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3828,22 +3818,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3854,31 +3844,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046833</t>
+          <t>https://artportalen.se/Sighting/137070028</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137070028</v>
+        <v>137070030</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401655</v>
+        <v>401585</v>
       </c>
       <c r="R30" t="n">
-        <v>6818195</v>
+        <v>6818203</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3991,16 +3991,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070028</t>
+          <t>https://artportalen.se/Sighting/137070030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137070030</v>
+        <v>137070036</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401585</v>
+        <v>401434</v>
       </c>
       <c r="R31" t="n">
-        <v>6818203</v>
+        <v>6818304</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,16 +4113,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070030</t>
+          <t>https://artportalen.se/Sighting/137070036</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137070036</v>
+        <v>137070038</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401434</v>
+        <v>401421</v>
       </c>
       <c r="R32" t="n">
-        <v>6818304</v>
+        <v>6818331</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,16 +4235,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070036</t>
+          <t>https://artportalen.se/Sighting/137070038</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137070038</v>
+        <v>137070058</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4276,13 +4276,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401421</v>
+        <v>401424</v>
       </c>
       <c r="R33" t="n">
-        <v>6818331</v>
+        <v>6818182</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Bark on living woody plant</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4357,16 +4357,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070038</t>
+          <t>https://artportalen.se/Sighting/137070058</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137070058</v>
+        <v>137070061</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401424</v>
+        <v>401558</v>
       </c>
       <c r="R34" t="n">
-        <v>6818182</v>
+        <v>6818089</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant</t>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4479,16 +4479,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070058</t>
+          <t>https://artportalen.se/Sighting/137070061</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137070061</v>
+        <v>137070068</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401558</v>
+        <v>401309</v>
       </c>
       <c r="R35" t="n">
-        <v>6818089</v>
+        <v>6817921</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4601,16 +4601,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070061</t>
+          <t>https://artportalen.se/Sighting/137070068</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137070068</v>
+        <v>137070069</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401309</v>
+        <v>401307</v>
       </c>
       <c r="R36" t="n">
-        <v>6817921</v>
+        <v>6817938</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4687,7 +4687,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en 30 meters radie</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,16 +4728,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070068</t>
+          <t>https://artportalen.se/Sighting/137070069</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137070069</v>
+        <v>137070070</v>
       </c>
       <c r="B37" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4758,19 +4763,20 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401307</v>
+        <v>401301</v>
       </c>
       <c r="R37" t="n">
-        <v>6817938</v>
+        <v>6817945</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4799,7 +4805,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4809,12 +4815,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en 30 meters radie</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4850,16 +4851,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070069</t>
+          <t>https://artportalen.se/Sighting/137070070</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137070070</v>
+        <v>137070073</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4885,20 +4886,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401301</v>
+        <v>401198</v>
       </c>
       <c r="R38" t="n">
-        <v>6817945</v>
+        <v>6818027</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4973,16 +4973,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070070</t>
+          <t>https://artportalen.se/Sighting/137070073</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137070073</v>
+        <v>137070076</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401198</v>
+        <v>401336</v>
       </c>
       <c r="R39" t="n">
-        <v>6818027</v>
+        <v>6818033</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree</t>
+          <t>Bark on living woody plant</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5095,16 +5095,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070073</t>
+          <t>https://artportalen.se/Sighting/137070076</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137070076</v>
+        <v>137071204</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>401336</v>
+        <v>401619</v>
       </c>
       <c r="R40" t="n">
-        <v>6818033</v>
+        <v>6818175</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,41 +5192,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070076</t>
+          <t>https://artportalen.se/Sighting/137071204</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137071204</v>
+        <v>137071205</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5258,13 +5248,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>401619</v>
+        <v>401554</v>
       </c>
       <c r="R41" t="n">
-        <v>6818175</v>
+        <v>6818238</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5293,7 +5283,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5303,7 +5293,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5329,16 +5319,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071204</t>
+          <t>https://artportalen.se/Sighting/137071205</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137071205</v>
+        <v>137071209</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,13 +5360,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>401554</v>
+        <v>401464</v>
       </c>
       <c r="R42" t="n">
-        <v>6818238</v>
+        <v>6818308</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5405,7 +5395,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5415,7 +5405,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5441,16 +5431,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071205</t>
+          <t>https://artportalen.se/Sighting/137071209</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137071209</v>
+        <v>137071218</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5482,13 +5472,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>401464</v>
+        <v>401354</v>
       </c>
       <c r="R43" t="n">
-        <v>6818308</v>
+        <v>6818369</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5517,7 +5507,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5527,7 +5517,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,16 +5543,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071209</t>
+          <t>https://artportalen.se/Sighting/137071218</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137071218</v>
+        <v>137071229</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5594,13 +5584,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>401354</v>
+        <v>401326</v>
       </c>
       <c r="R44" t="n">
-        <v>6818369</v>
+        <v>6818360</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5629,7 +5619,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5639,7 +5629,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5665,16 +5655,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071218</t>
+          <t>https://artportalen.se/Sighting/137071229</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137071229</v>
+        <v>137071247</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5706,10 +5696,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>401326</v>
+        <v>401472</v>
       </c>
       <c r="R45" t="n">
-        <v>6818360</v>
+        <v>6818178</v>
       </c>
       <c r="S45" t="n">
         <v>7</v>
@@ -5741,7 +5731,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5751,7 +5741,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5777,16 +5767,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071229</t>
+          <t>https://artportalen.se/Sighting/137071247</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137071247</v>
+        <v>137071253</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5818,13 +5808,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>401472</v>
+        <v>401576</v>
       </c>
       <c r="R46" t="n">
-        <v>6818178</v>
+        <v>6818044</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5853,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5863,7 +5853,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5889,16 +5879,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071247</t>
+          <t>https://artportalen.se/Sighting/137071253</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137071253</v>
+        <v>137071257</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5924,19 +5914,20 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>401576</v>
+        <v>401644</v>
       </c>
       <c r="R47" t="n">
-        <v>6818044</v>
+        <v>6818020</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5965,7 +5956,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5975,7 +5966,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6001,16 +5992,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071253</t>
+          <t>https://artportalen.se/Sighting/137071257</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137071257</v>
+        <v>137071258</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6036,20 +6027,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>401644</v>
+        <v>401656</v>
       </c>
       <c r="R48" t="n">
-        <v>6818020</v>
+        <v>6818003</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6078,7 +6068,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6088,7 +6078,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6114,16 +6104,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071257</t>
+          <t>https://artportalen.se/Sighting/137071258</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137071258</v>
+        <v>137071259</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6155,13 +6145,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>401656</v>
+        <v>401665</v>
       </c>
       <c r="R49" t="n">
-        <v>6818003</v>
+        <v>6817990</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6190,7 +6180,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6200,7 +6190,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6226,16 +6216,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071258</t>
+          <t>https://artportalen.se/Sighting/137071259</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137071259</v>
+        <v>137071262</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,13 +6257,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>401665</v>
+        <v>401462</v>
       </c>
       <c r="R50" t="n">
-        <v>6817990</v>
+        <v>6817966</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6302,7 +6292,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6312,7 +6302,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6338,16 +6328,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071259</t>
+          <t>https://artportalen.se/Sighting/137071262</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137071262</v>
+        <v>137071265</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,19 +6363,20 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>401462</v>
+        <v>401412</v>
       </c>
       <c r="R51" t="n">
-        <v>6817966</v>
+        <v>6817926</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6414,7 +6405,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6424,7 +6415,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6450,16 +6441,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071262</t>
+          <t>https://artportalen.se/Sighting/137071265</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137071265</v>
+        <v>137071267</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6485,20 +6476,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>401412</v>
+        <v>401371</v>
       </c>
       <c r="R52" t="n">
-        <v>6817926</v>
+        <v>6817915</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6527,7 +6517,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6537,7 +6527,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6563,16 +6553,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071265</t>
+          <t>https://artportalen.se/Sighting/137071267</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137071267</v>
+        <v>137071271</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6604,13 +6594,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>401371</v>
+        <v>401320</v>
       </c>
       <c r="R53" t="n">
-        <v>6817915</v>
+        <v>6817898</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6639,7 +6629,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6649,7 +6639,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6675,16 +6665,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071267</t>
+          <t>https://artportalen.se/Sighting/137071271</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137071271</v>
+        <v>137071272</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6710,19 +6700,20 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>401320</v>
+        <v>401325</v>
       </c>
       <c r="R54" t="n">
-        <v>6817898</v>
+        <v>6817913</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6751,7 +6742,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6761,7 +6752,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6787,16 +6778,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071271</t>
+          <t>https://artportalen.se/Sighting/137071272</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137071272</v>
+        <v>137071275</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6822,20 +6813,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>401325</v>
+        <v>401309</v>
       </c>
       <c r="R55" t="n">
-        <v>6817913</v>
+        <v>6817948</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6864,7 +6854,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6874,7 +6864,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6900,16 +6890,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071272</t>
+          <t>https://artportalen.se/Sighting/137071275</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137071275</v>
+        <v>137071278</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6941,13 +6931,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>401309</v>
+        <v>401295</v>
       </c>
       <c r="R56" t="n">
-        <v>6817948</v>
+        <v>6817963</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6976,7 +6966,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6986,7 +6976,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7012,16 +7002,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071275</t>
+          <t>https://artportalen.se/Sighting/137071278</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137071278</v>
+        <v>137071279</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7053,10 +7043,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>401295</v>
+        <v>401288</v>
       </c>
       <c r="R57" t="n">
-        <v>6817963</v>
+        <v>6817995</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7088,7 +7078,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7098,7 +7088,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7124,16 +7114,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071278</t>
+          <t>https://artportalen.se/Sighting/137071279</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137071279</v>
+        <v>137071281</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7165,13 +7155,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>401288</v>
+        <v>401258</v>
       </c>
       <c r="R58" t="n">
-        <v>6817995</v>
+        <v>6818033</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7200,7 +7190,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7210,7 +7200,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7236,16 +7226,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071279</t>
+          <t>https://artportalen.se/Sighting/137071281</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137071281</v>
+        <v>137071282</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7277,13 +7267,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>401258</v>
+        <v>401220</v>
       </c>
       <c r="R59" t="n">
-        <v>6818033</v>
+        <v>6818026</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7312,7 +7302,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7322,7 +7312,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7348,16 +7343,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071281</t>
+          <t>https://artportalen.se/Sighting/137071282</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137071282</v>
+        <v>137071286</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7389,13 +7384,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>401220</v>
+        <v>401202</v>
       </c>
       <c r="R60" t="n">
-        <v>6818026</v>
+        <v>6818014</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7424,7 +7419,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7434,12 +7429,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7465,16 +7455,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071282</t>
+          <t>https://artportalen.se/Sighting/137071286</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137071286</v>
+        <v>137071288</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,13 +7496,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>401202</v>
+        <v>401188</v>
       </c>
       <c r="R61" t="n">
-        <v>6818014</v>
+        <v>6818024</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7541,7 +7531,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7551,7 +7541,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7577,16 +7567,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071286</t>
+          <t>https://artportalen.se/Sighting/137071288</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137071288</v>
+        <v>137071290</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7621,7 +7611,7 @@
         <v>401188</v>
       </c>
       <c r="R62" t="n">
-        <v>6818024</v>
+        <v>6818057</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7653,7 +7643,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7663,7 +7653,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7689,16 +7679,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071288</t>
+          <t>https://artportalen.se/Sighting/137071290</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137071290</v>
+        <v>137071291</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7730,13 +7720,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>401188</v>
+        <v>401254</v>
       </c>
       <c r="R63" t="n">
-        <v>6818057</v>
+        <v>6818041</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7765,7 +7755,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7775,7 +7765,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7801,16 +7791,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071290</t>
+          <t>https://artportalen.se/Sighting/137071291</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137071291</v>
+        <v>137071293</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7842,13 +7832,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>401254</v>
+        <v>401318</v>
       </c>
       <c r="R64" t="n">
-        <v>6818041</v>
+        <v>6818035</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7877,7 +7867,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7887,7 +7877,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7913,16 +7903,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071291</t>
+          <t>https://artportalen.se/Sighting/137071293</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137071293</v>
+        <v>137071294</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7954,13 +7944,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>401318</v>
+        <v>401377</v>
       </c>
       <c r="R65" t="n">
-        <v>6818035</v>
+        <v>6818058</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7989,7 +7979,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7999,7 +7989,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8025,38 +8015,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071293</t>
+          <t>https://artportalen.se/Sighting/137071294</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137071294</v>
+        <v>131047033</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>78730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8066,13 +8056,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>401377</v>
+        <v>401560</v>
       </c>
       <c r="R66" t="n">
-        <v>6818058</v>
+        <v>6817813</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8096,22 +8086,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8126,24 +8116,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071294</t>
+          <t>https://artportalen.se/Sighting/131047033</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131047033</v>
+        <v>131047034</v>
       </c>
       <c r="B67" t="n">
         <v>78730</v>
@@ -8178,10 +8168,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>401560</v>
+        <v>401597</v>
       </c>
       <c r="R67" t="n">
-        <v>6817813</v>
+        <v>6817852</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8213,7 +8203,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8223,7 +8213,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8249,16 +8239,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131047033</t>
+          <t>https://artportalen.se/Sighting/131047034</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131047034</v>
+        <v>137071220</v>
       </c>
       <c r="B68" t="n">
-        <v>78730</v>
+        <v>78924</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8290,13 +8280,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>401597</v>
+        <v>401349</v>
       </c>
       <c r="R68" t="n">
-        <v>6817852</v>
+        <v>6818407</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8320,22 +8310,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8346,31 +8336,41 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131047034</t>
+          <t>https://artportalen.se/Sighting/137071220</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137071220</v>
+        <v>137071232</v>
       </c>
       <c r="B69" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8402,13 +8402,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>401349</v>
+        <v>401348</v>
       </c>
       <c r="R69" t="n">
-        <v>6818407</v>
+        <v>6818297</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8483,16 +8483,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071220</t>
+          <t>https://artportalen.se/Sighting/137071232</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137071232</v>
+        <v>137071234</v>
       </c>
       <c r="B70" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>401348</v>
+        <v>401319</v>
       </c>
       <c r="R70" t="n">
-        <v>6818297</v>
+        <v>6818281</v>
       </c>
       <c r="S70" t="n">
         <v>9</v>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8605,16 +8605,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071232</t>
+          <t>https://artportalen.se/Sighting/137071234</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137071234</v>
+        <v>131046708</v>
       </c>
       <c r="B71" t="n">
-        <v>78919</v>
+        <v>83307</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8622,21 +8622,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8646,13 +8646,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>401319</v>
+        <v>401645</v>
       </c>
       <c r="R71" t="n">
-        <v>6818281</v>
+        <v>6818016</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8676,22 +8676,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8702,38 +8702,28 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071234</t>
+          <t>https://artportalen.se/Sighting/131046708</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131046708</v>
+        <v>131046709</v>
       </c>
       <c r="B72" t="n">
         <v>83307</v>
@@ -8768,10 +8758,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>401645</v>
+        <v>401646</v>
       </c>
       <c r="R72" t="n">
-        <v>6818016</v>
+        <v>6817967</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8803,7 +8793,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8813,7 +8803,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8839,16 +8829,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046708</t>
+          <t>https://artportalen.se/Sighting/131046709</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131046709</v>
+        <v>137071210</v>
       </c>
       <c r="B73" t="n">
-        <v>83307</v>
+        <v>83512</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8880,13 +8870,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>401646</v>
+        <v>401466</v>
       </c>
       <c r="R73" t="n">
-        <v>6817967</v>
+        <v>6818300</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8910,22 +8900,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8934,33 +8924,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046709</t>
+          <t>https://artportalen.se/Sighting/137071210</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137071210</v>
+        <v>137070048</v>
       </c>
       <c r="B74" t="n">
-        <v>83507</v>
+        <v>79278</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8968,21 +8959,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8992,13 +8983,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>401466</v>
+        <v>401333</v>
       </c>
       <c r="R74" t="n">
-        <v>6818300</v>
+        <v>6818239</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9027,7 +9018,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9037,7 +9028,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9046,34 +9037,43 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071210</t>
+          <t>https://artportalen.se/Sighting/137070048</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137070048</v>
+        <v>137070059</v>
       </c>
       <c r="B75" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>401333</v>
+        <v>401489</v>
       </c>
       <c r="R75" t="n">
-        <v>6818239</v>
+        <v>6818079</v>
       </c>
       <c r="S75" t="n">
         <v>7</v>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9186,16 +9186,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070048</t>
+          <t>https://artportalen.se/Sighting/137070059</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137070059</v>
+        <v>137070064</v>
       </c>
       <c r="B76" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>401489</v>
+        <v>401559</v>
       </c>
       <c r="R76" t="n">
-        <v>6818079</v>
+        <v>6818052</v>
       </c>
       <c r="S76" t="n">
         <v>7</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9308,16 +9308,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070059</t>
+          <t>https://artportalen.se/Sighting/137070064</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137070064</v>
+        <v>137071239</v>
       </c>
       <c r="B77" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9349,13 +9349,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>401559</v>
+        <v>401388</v>
       </c>
       <c r="R77" t="n">
-        <v>6818052</v>
+        <v>6818236</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9408,38 +9408,38 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070064</t>
+          <t>https://artportalen.se/Sighting/137071239</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137071239</v>
+        <v>137071249</v>
       </c>
       <c r="B78" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9471,13 +9471,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>401388</v>
+        <v>401548</v>
       </c>
       <c r="R78" t="n">
-        <v>6818236</v>
+        <v>6818050</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9552,16 +9552,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071239</t>
+          <t>https://artportalen.se/Sighting/137071249</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137071249</v>
+        <v>137071251</v>
       </c>
       <c r="B79" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9593,13 +9593,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>401548</v>
+        <v>401576</v>
       </c>
       <c r="R79" t="n">
-        <v>6818050</v>
+        <v>6818058</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9674,16 +9674,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071249</t>
+          <t>https://artportalen.se/Sighting/137071251</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137071251</v>
+        <v>137070047</v>
       </c>
       <c r="B80" t="n">
-        <v>79273</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9691,21 +9691,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9715,13 +9715,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>401576</v>
+        <v>401317</v>
       </c>
       <c r="R80" t="n">
-        <v>6818058</v>
+        <v>6818298</v>
       </c>
       <c r="S80" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9774,38 +9774,38 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Fire killed tree</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071251</t>
+          <t>https://artportalen.se/Sighting/137070047</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137070047</v>
+        <v>137070049</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9837,13 +9837,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>401317</v>
+        <v>401345</v>
       </c>
       <c r="R81" t="n">
-        <v>6818298</v>
+        <v>6818219</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9918,16 +9918,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070047</t>
+          <t>https://artportalen.se/Sighting/137070049</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137070049</v>
+        <v>137070050</v>
       </c>
       <c r="B82" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9959,13 +9959,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>401345</v>
+        <v>401313</v>
       </c>
       <c r="R82" t="n">
-        <v>6818219</v>
+        <v>6818186</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10040,16 +10040,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070049</t>
+          <t>https://artportalen.se/Sighting/137070050</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137070050</v>
+        <v>137070051</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10081,13 +10081,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>401313</v>
+        <v>401392</v>
       </c>
       <c r="R83" t="n">
-        <v>6818186</v>
+        <v>6818205</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10162,16 +10162,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070050</t>
+          <t>https://artportalen.se/Sighting/137070051</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137070051</v>
+        <v>137070054</v>
       </c>
       <c r="B84" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>401392</v>
+        <v>401384</v>
       </c>
       <c r="R84" t="n">
-        <v>6818205</v>
+        <v>6818197</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10284,16 +10284,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070051</t>
+          <t>https://artportalen.se/Sighting/137070054</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>137070054</v>
+        <v>137070056</v>
       </c>
       <c r="B85" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,13 +10325,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>401384</v>
+        <v>401378</v>
       </c>
       <c r="R85" t="n">
-        <v>6818197</v>
+        <v>6818176</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10406,16 +10406,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070054</t>
+          <t>https://artportalen.se/Sighting/137070056</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137070056</v>
+        <v>137070060</v>
       </c>
       <c r="B86" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10447,13 +10447,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>401378</v>
+        <v>401489</v>
       </c>
       <c r="R86" t="n">
-        <v>6818176</v>
+        <v>6818079</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10528,16 +10528,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070056</t>
+          <t>https://artportalen.se/Sighting/137070060</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137070060</v>
+        <v>137070065</v>
       </c>
       <c r="B87" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>401489</v>
+        <v>401559</v>
       </c>
       <c r="R87" t="n">
-        <v>6818079</v>
+        <v>6818052</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10650,16 +10650,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070060</t>
+          <t>https://artportalen.se/Sighting/137070065</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137070065</v>
+        <v>137071213</v>
       </c>
       <c r="B88" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10691,13 +10691,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>401559</v>
+        <v>401394</v>
       </c>
       <c r="R88" t="n">
-        <v>6818052</v>
+        <v>6818347</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10750,38 +10750,38 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070065</t>
+          <t>https://artportalen.se/Sighting/137071213</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137071213</v>
+        <v>137071219</v>
       </c>
       <c r="B89" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10813,13 +10813,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>401394</v>
+        <v>401347</v>
       </c>
       <c r="R89" t="n">
-        <v>6818347</v>
+        <v>6818408</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10869,16 +10869,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10894,16 +10884,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071213</t>
+          <t>https://artportalen.se/Sighting/137071219</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137071219</v>
+        <v>137071224</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10935,13 +10925,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>401347</v>
+        <v>401335</v>
       </c>
       <c r="R90" t="n">
-        <v>6818408</v>
+        <v>6818436</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10970,7 +10960,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10980,7 +10970,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11006,16 +10996,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071219</t>
+          <t>https://artportalen.se/Sighting/137071224</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137071224</v>
+        <v>137071225</v>
       </c>
       <c r="B91" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11047,13 +11037,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>401335</v>
+        <v>401322</v>
       </c>
       <c r="R91" t="n">
-        <v>6818436</v>
+        <v>6818399</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11082,7 +11072,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11092,7 +11082,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11118,16 +11108,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071224</t>
+          <t>https://artportalen.se/Sighting/137071225</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137071225</v>
+        <v>137071230</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11159,13 +11149,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>401322</v>
+        <v>401344</v>
       </c>
       <c r="R92" t="n">
-        <v>6818399</v>
+        <v>6818345</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11194,7 +11184,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11204,7 +11194,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11230,16 +11220,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071225</t>
+          <t>https://artportalen.se/Sighting/137071230</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137071230</v>
+        <v>137071231</v>
       </c>
       <c r="B93" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11271,13 +11261,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>401344</v>
+        <v>401351</v>
       </c>
       <c r="R93" t="n">
-        <v>6818345</v>
+        <v>6818323</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11306,7 +11296,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11316,7 +11306,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11342,16 +11332,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071230</t>
+          <t>https://artportalen.se/Sighting/137071231</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137071231</v>
+        <v>137071250</v>
       </c>
       <c r="B94" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11383,13 +11373,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>401351</v>
+        <v>401548</v>
       </c>
       <c r="R94" t="n">
-        <v>6818323</v>
+        <v>6818050</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11418,7 +11408,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11428,7 +11418,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11439,6 +11429,16 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11454,16 +11454,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071231</t>
+          <t>https://artportalen.se/Sighting/137071250</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137071250</v>
+        <v>137071252</v>
       </c>
       <c r="B95" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>401548</v>
+        <v>401576</v>
       </c>
       <c r="R95" t="n">
-        <v>6818050</v>
+        <v>6818058</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11576,16 +11576,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071250</t>
+          <t>https://artportalen.se/Sighting/137071252</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137071252</v>
+        <v>137071256</v>
       </c>
       <c r="B96" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>401576</v>
+        <v>401632</v>
       </c>
       <c r="R96" t="n">
-        <v>6818058</v>
+        <v>6818078</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11673,16 +11673,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11698,16 +11688,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071252</t>
+          <t>https://artportalen.se/Sighting/137071256</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137071256</v>
+        <v>137071264</v>
       </c>
       <c r="B97" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11739,13 +11729,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>401632</v>
+        <v>401414</v>
       </c>
       <c r="R97" t="n">
-        <v>6818078</v>
+        <v>6817944</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11774,7 +11764,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11784,7 +11774,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11795,6 +11785,16 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11810,16 +11810,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071256</t>
+          <t>https://artportalen.se/Sighting/137071264</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137071264</v>
+        <v>137071266</v>
       </c>
       <c r="B98" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>401414</v>
+        <v>401375</v>
       </c>
       <c r="R98" t="n">
-        <v>6817944</v>
+        <v>6817917</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11932,16 +11932,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071264</t>
+          <t>https://artportalen.se/Sighting/137071266</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137071266</v>
+        <v>137071268</v>
       </c>
       <c r="B99" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11973,10 +11973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>401375</v>
+        <v>401355</v>
       </c>
       <c r="R99" t="n">
-        <v>6817917</v>
+        <v>6817896</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12054,16 +12054,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071266</t>
+          <t>https://artportalen.se/Sighting/137071268</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137071268</v>
+        <v>131047032</v>
       </c>
       <c r="B100" t="n">
-        <v>80135</v>
+        <v>78334</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12071,21 +12071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12095,13 +12095,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>401355</v>
+        <v>401560</v>
       </c>
       <c r="R100" t="n">
-        <v>6817896</v>
+        <v>6817813</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12125,22 +12125,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12151,41 +12151,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071268</t>
+          <t>https://artportalen.se/Sighting/131047032</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131047032</v>
+        <v>137071261</v>
       </c>
       <c r="B101" t="n">
-        <v>78334</v>
+        <v>78521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12217,13 +12207,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>401560</v>
+        <v>401488</v>
       </c>
       <c r="R101" t="n">
-        <v>6817813</v>
+        <v>6817975</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12247,22 +12237,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12273,66 +12263,77 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131047032</t>
+          <t>https://artportalen.se/Sighting/137071261</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137071261</v>
+        <v>137071277</v>
       </c>
       <c r="B102" t="n">
-        <v>78516</v>
+        <v>58032</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>401488</v>
+        <v>401299</v>
       </c>
       <c r="R102" t="n">
-        <v>6817975</v>
+        <v>6817937</v>
       </c>
       <c r="S102" t="n">
         <v>7</v>
@@ -12364,7 +12365,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12374,7 +12375,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12385,16 +12386,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -12410,33 +12401,33 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071261</t>
+          <t>https://artportalen.se/Sighting/137071277</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137071277</v>
+        <v>137071199</v>
       </c>
       <c r="B103" t="n">
-        <v>58031</v>
+        <v>58149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>100090</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -12452,13 +12443,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>401299</v>
+        <v>401637</v>
       </c>
       <c r="R103" t="n">
-        <v>6817937</v>
+        <v>6818171</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12487,7 +12478,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12497,7 +12488,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12523,16 +12514,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071277</t>
+          <t>https://artportalen.se/Sighting/137071199</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137071199</v>
+        <v>131046765</v>
       </c>
       <c r="B104" t="n">
-        <v>58148</v>
+        <v>57953</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12540,16 +12531,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100090</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -12558,20 +12549,27 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>401637</v>
+        <v>401702</v>
       </c>
       <c r="R104" t="n">
-        <v>6818171</v>
+        <v>6818073</v>
       </c>
       <c r="S104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12595,22 +12593,27 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12625,24 +12628,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071199</t>
+          <t>https://artportalen.se/Sighting/131046765</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131046765</v>
+        <v>131046766</v>
       </c>
       <c r="B105" t="n">
         <v>57953</v>
@@ -12685,10 +12688,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>401702</v>
+        <v>401318</v>
       </c>
       <c r="R105" t="n">
-        <v>6818073</v>
+        <v>6818379</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12720,7 +12723,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12730,7 +12733,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -12761,13 +12764,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046765</t>
+          <t>https://artportalen.se/Sighting/131046766</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131046766</v>
+        <v>131046768</v>
       </c>
       <c r="B106" t="n">
         <v>57953</v>
@@ -12796,24 +12799,21 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>401318</v>
+        <v>401346</v>
       </c>
       <c r="R106" t="n">
-        <v>6818379</v>
+        <v>6818439</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>Både färska och gamla ringhack på grov gammal tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12886,13 +12886,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046766</t>
+          <t>https://artportalen.se/Sighting/131046768</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131046768</v>
+        <v>131046769</v>
       </c>
       <c r="B107" t="n">
         <v>57953</v>
@@ -12932,10 +12932,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>401346</v>
+        <v>401575</v>
       </c>
       <c r="R107" t="n">
-        <v>6818439</v>
+        <v>6817873</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Både färska och gamla ringhack på grov gammal tall</t>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13008,13 +13008,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046768</t>
+          <t>https://artportalen.se/Sighting/131046769</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131046769</v>
+        <v>131046770</v>
       </c>
       <c r="B108" t="n">
         <v>57953</v>
@@ -13054,10 +13054,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>401575</v>
+        <v>401576</v>
       </c>
       <c r="R108" t="n">
-        <v>6817873</v>
+        <v>6817907</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -13130,13 +13130,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046769</t>
+          <t>https://artportalen.se/Sighting/131046770</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131046770</v>
+        <v>131046771</v>
       </c>
       <c r="B109" t="n">
         <v>57953</v>
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>401576</v>
+        <v>401556</v>
       </c>
       <c r="R109" t="n">
-        <v>6817907</v>
+        <v>6817954</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -13252,13 +13252,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046770</t>
+          <t>https://artportalen.se/Sighting/131046771</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131046771</v>
+        <v>131046772</v>
       </c>
       <c r="B110" t="n">
         <v>57953</v>
@@ -13298,10 +13298,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>401556</v>
+        <v>401507</v>
       </c>
       <c r="R110" t="n">
-        <v>6817954</v>
+        <v>6818011</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13374,13 +13374,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046771</t>
+          <t>https://artportalen.se/Sighting/131046772</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131046772</v>
+        <v>131046773</v>
       </c>
       <c r="B111" t="n">
         <v>57953</v>
@@ -13411,7 +13411,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13420,10 +13420,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>401507</v>
+        <v>401346</v>
       </c>
       <c r="R111" t="n">
-        <v>6818011</v>
+        <v>6818162</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack (tall)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13496,13 +13496,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046772</t>
+          <t>https://artportalen.se/Sighting/131046773</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131046773</v>
+        <v>131047013</v>
       </c>
       <c r="B112" t="n">
         <v>57953</v>
@@ -13533,7 +13533,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>401346</v>
+        <v>401631</v>
       </c>
       <c r="R112" t="n">
-        <v>6818162</v>
+        <v>6817903</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13587,19 +13587,19 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
         </is>
       </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG112" t="b">
         <v>0</v>
@@ -13618,13 +13618,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046773</t>
+          <t>https://artportalen.se/Sighting/131047013</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131047013</v>
+        <v>131047014</v>
       </c>
       <c r="B113" t="n">
         <v>57953</v>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>401631</v>
+        <v>401378</v>
       </c>
       <c r="R113" t="n">
-        <v>6817903</v>
+        <v>6818082</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -13740,16 +13740,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131047013</t>
+          <t>https://artportalen.se/Sighting/131047014</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131047014</v>
+        <v>137070033</v>
       </c>
       <c r="B114" t="n">
-        <v>57953</v>
+        <v>58035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13775,24 +13775,20 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>401378</v>
+        <v>401430</v>
       </c>
       <c r="R114" t="n">
-        <v>6818082</v>
+        <v>6818303</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13816,34 +13812,29 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Troliga spår efter tretåig hackspett (barkfälkning)</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -13851,27 +13842,27 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131047014</t>
+          <t>https://artportalen.se/Sighting/137070033</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>137070033</v>
+        <v>137070039</v>
       </c>
       <c r="B115" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13904,13 +13895,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>401430</v>
+        <v>401408</v>
       </c>
       <c r="R115" t="n">
-        <v>6818303</v>
+        <v>6818350</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13939,7 +13930,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13949,7 +13940,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13975,16 +13966,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070033</t>
+          <t>https://artportalen.se/Sighting/137070039</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>137070039</v>
+        <v>137070044</v>
       </c>
       <c r="B116" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14017,13 +14008,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>401408</v>
+        <v>401361</v>
       </c>
       <c r="R116" t="n">
-        <v>6818350</v>
+        <v>6818440</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14052,7 +14043,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14062,7 +14053,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14088,16 +14079,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070039</t>
+          <t>https://artportalen.se/Sighting/137070044</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>137070044</v>
+        <v>137070062</v>
       </c>
       <c r="B117" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14130,13 +14121,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>401361</v>
+        <v>401545</v>
       </c>
       <c r="R117" t="n">
-        <v>6818440</v>
+        <v>6818047</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14165,7 +14156,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14175,7 +14166,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14201,16 +14192,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070044</t>
+          <t>https://artportalen.se/Sighting/137070062</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>137070062</v>
+        <v>137070071</v>
       </c>
       <c r="B118" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14243,10 +14234,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>401545</v>
+        <v>401296</v>
       </c>
       <c r="R118" t="n">
-        <v>6818047</v>
+        <v>6818004</v>
       </c>
       <c r="S118" t="n">
         <v>7</v>
@@ -14278,7 +14269,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14288,7 +14279,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14314,16 +14305,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070062</t>
+          <t>https://artportalen.se/Sighting/137070071</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>137070071</v>
+        <v>137070075</v>
       </c>
       <c r="B119" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14356,13 +14347,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>401296</v>
+        <v>401336</v>
       </c>
       <c r="R119" t="n">
-        <v>6818004</v>
+        <v>6818028</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14391,7 +14382,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14401,7 +14392,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14427,16 +14418,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070071</t>
+          <t>https://artportalen.se/Sighting/137070075</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>137070075</v>
+        <v>137071228</v>
       </c>
       <c r="B120" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14469,13 +14460,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>401336</v>
+        <v>401315</v>
       </c>
       <c r="R120" t="n">
-        <v>6818028</v>
+        <v>6818380</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14504,7 +14495,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14514,7 +14505,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14529,27 +14520,27 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070075</t>
+          <t>https://artportalen.se/Sighting/137071228</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>137071228</v>
+        <v>137071236</v>
       </c>
       <c r="B121" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14582,10 +14573,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>401315</v>
+        <v>401319</v>
       </c>
       <c r="R121" t="n">
-        <v>6818380</v>
+        <v>6818273</v>
       </c>
       <c r="S121" t="n">
         <v>8</v>
@@ -14617,7 +14608,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14627,7 +14618,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14653,16 +14644,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071228</t>
+          <t>https://artportalen.se/Sighting/137071236</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137071236</v>
+        <v>137071237</v>
       </c>
       <c r="B122" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14695,13 +14686,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>401319</v>
+        <v>401330</v>
       </c>
       <c r="R122" t="n">
-        <v>6818273</v>
+        <v>6818228</v>
       </c>
       <c r="S122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14730,7 +14721,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14740,7 +14731,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14766,16 +14757,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071236</t>
+          <t>https://artportalen.se/Sighting/137071237</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137071237</v>
+        <v>137071241</v>
       </c>
       <c r="B123" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14808,10 +14799,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>401330</v>
+        <v>401420</v>
       </c>
       <c r="R123" t="n">
-        <v>6818228</v>
+        <v>6818232</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14843,7 +14834,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14853,7 +14844,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14879,16 +14870,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071237</t>
+          <t>https://artportalen.se/Sighting/137071241</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137071241</v>
+        <v>137071245</v>
       </c>
       <c r="B124" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14921,13 +14912,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>401420</v>
+        <v>401472</v>
       </c>
       <c r="R124" t="n">
-        <v>6818232</v>
+        <v>6818201</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14956,7 +14947,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14966,7 +14957,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14992,16 +14983,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071241</t>
+          <t>https://artportalen.se/Sighting/137071245</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>137071245</v>
+        <v>137071248</v>
       </c>
       <c r="B125" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15034,13 +15025,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>401472</v>
+        <v>401597</v>
       </c>
       <c r="R125" t="n">
-        <v>6818201</v>
+        <v>6818095</v>
       </c>
       <c r="S125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -15069,7 +15060,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15079,7 +15070,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15105,16 +15096,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071245</t>
+          <t>https://artportalen.se/Sighting/137071248</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137071248</v>
+        <v>137071255</v>
       </c>
       <c r="B126" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15147,13 +15138,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>401597</v>
+        <v>401620</v>
       </c>
       <c r="R126" t="n">
-        <v>6818095</v>
+        <v>6818079</v>
       </c>
       <c r="S126" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15182,7 +15173,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15192,7 +15183,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15218,16 +15209,16 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071248</t>
+          <t>https://artportalen.se/Sighting/137071255</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>137071255</v>
+        <v>137071280</v>
       </c>
       <c r="B127" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15260,13 +15251,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>401620</v>
+        <v>401286</v>
       </c>
       <c r="R127" t="n">
-        <v>6818079</v>
+        <v>6817998</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15295,7 +15286,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15305,7 +15296,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15331,16 +15322,16 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071255</t>
+          <t>https://artportalen.se/Sighting/137071280</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>137071280</v>
+        <v>137071284</v>
       </c>
       <c r="B128" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15373,13 +15364,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>401286</v>
+        <v>401198</v>
       </c>
       <c r="R128" t="n">
         <v>6817998</v>
       </c>
       <c r="S128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15408,7 +15399,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15418,7 +15409,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15444,16 +15435,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071280</t>
+          <t>https://artportalen.se/Sighting/137071284</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>137071284</v>
+        <v>137071295</v>
       </c>
       <c r="B129" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15486,10 +15477,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>401198</v>
+        <v>401398</v>
       </c>
       <c r="R129" t="n">
-        <v>6817998</v>
+        <v>6818062</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -15521,7 +15512,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15531,7 +15522,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15557,16 +15548,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071284</t>
+          <t>https://artportalen.se/Sighting/137071295</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>137071295</v>
+        <v>137070041</v>
       </c>
       <c r="B130" t="n">
-        <v>58034</v>
+        <v>58196</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15574,21 +15565,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15599,10 +15590,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>401398</v>
+        <v>401369</v>
       </c>
       <c r="R130" t="n">
-        <v>6818062</v>
+        <v>6818364</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -15634,7 +15625,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15644,7 +15635,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15659,27 +15650,27 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071295</t>
+          <t>https://artportalen.se/Sighting/137070041</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>137070041</v>
+        <v>137071201</v>
       </c>
       <c r="B131" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15712,13 +15703,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>401369</v>
+        <v>401656</v>
       </c>
       <c r="R131" t="n">
-        <v>6818364</v>
+        <v>6818165</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15747,7 +15738,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15757,7 +15748,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15772,27 +15763,27 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070041</t>
+          <t>https://artportalen.se/Sighting/137071201</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>137071201</v>
+        <v>137071235</v>
       </c>
       <c r="B132" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15818,17 +15809,20 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>401656</v>
+        <v>401317</v>
       </c>
       <c r="R132" t="n">
-        <v>6818165</v>
+        <v>6818282</v>
       </c>
       <c r="S132" t="n">
         <v>8</v>
@@ -15860,7 +15854,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15870,7 +15864,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Bohåla i hög björkstubbe.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15896,58 +15895,55 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071201</t>
+          <t>https://artportalen.se/Sighting/137071235</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>137071235</v>
+        <v>137070040</v>
       </c>
       <c r="B133" t="n">
-        <v>58195</v>
+        <v>8470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>401317</v>
+        <v>401370</v>
       </c>
       <c r="R133" t="n">
-        <v>6818282</v>
+        <v>6818372</v>
       </c>
       <c r="S133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15976,7 +15972,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15986,12 +15982,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Bohåla i hög björkstubbe.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16006,24 +15997,24 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071235</t>
+          <t>https://artportalen.se/Sighting/137070040</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>137070040</v>
+        <v>137071233</v>
       </c>
       <c r="B134" t="n">
         <v>8470</v>
@@ -16059,10 +16050,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>401370</v>
+        <v>401348</v>
       </c>
       <c r="R134" t="n">
-        <v>6818372</v>
+        <v>6818301</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16094,7 +16085,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16104,7 +16095,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16119,49 +16110,49 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070040</t>
+          <t>https://artportalen.se/Sighting/137071233</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>137071233</v>
+        <v>137071240</v>
       </c>
       <c r="B135" t="n">
-        <v>8470</v>
+        <v>56598</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>206004</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16172,13 +16163,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>401348</v>
+        <v>401412</v>
       </c>
       <c r="R135" t="n">
-        <v>6818301</v>
+        <v>6818218</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16207,7 +16198,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16217,7 +16208,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16243,13 +16234,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071233</t>
+          <t>https://artportalen.se/Sighting/137071240</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>137071240</v>
+        <v>137071276</v>
       </c>
       <c r="B136" t="n">
         <v>56598</v>
@@ -16285,13 +16276,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>401412</v>
+        <v>401299</v>
       </c>
       <c r="R136" t="n">
-        <v>6818218</v>
+        <v>6817946</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16320,7 +16311,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16330,7 +16321,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16356,55 +16347,54 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071240</t>
+          <t>https://artportalen.se/Sighting/137071276</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>137071276</v>
+        <v>137071287</v>
       </c>
       <c r="B137" t="n">
-        <v>56598</v>
+        <v>98280</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>206004</v>
+        <v>221945</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blomkällan, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>401299</v>
+        <v>401188</v>
       </c>
       <c r="R137" t="n">
-        <v>6817946</v>
+        <v>6818023</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16433,7 +16423,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16443,7 +16433,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16469,16 +16459,16 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071276</t>
+          <t>https://artportalen.se/Sighting/137071287</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137071287</v>
+        <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>98274</v>
+        <v>104144</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16486,16 +16476,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221945</v>
+        <v>223284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -16510,13 +16500,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>401188</v>
+        <v>401447</v>
       </c>
       <c r="R138" t="n">
-        <v>6818023</v>
+        <v>6817956</v>
       </c>
       <c r="S138" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16545,7 +16535,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16555,7 +16545,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16581,38 +16571,38 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071287</t>
+          <t>https://artportalen.se/Sighting/137071263</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>137071263</v>
+        <v>131046799</v>
       </c>
       <c r="B139" t="n">
-        <v>104138</v>
+        <v>78339</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>223284</v>
+        <v>228579</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16622,13 +16612,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>401447</v>
+        <v>401649</v>
       </c>
       <c r="R139" t="n">
-        <v>6817956</v>
+        <v>6818014</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16652,22 +16642,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16682,27 +16672,27 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071263</t>
+          <t>https://artportalen.se/Sighting/131046799</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>131046799</v>
+        <v>137070057</v>
       </c>
       <c r="B140" t="n">
-        <v>78339</v>
+        <v>79279</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16710,21 +16700,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16734,13 +16724,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>401649</v>
+        <v>401381</v>
       </c>
       <c r="R140" t="n">
-        <v>6818014</v>
+        <v>6818170</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16764,22 +16754,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16790,31 +16780,41 @@
       </c>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046799</t>
+          <t>https://artportalen.se/Sighting/137070057</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>137070057</v>
+        <v>137070063</v>
       </c>
       <c r="B141" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>401381</v>
+        <v>401559</v>
       </c>
       <c r="R141" t="n">
-        <v>6818170</v>
+        <v>6818052</v>
       </c>
       <c r="S141" t="n">
         <v>7</v>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16927,16 +16927,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070057</t>
+          <t>https://artportalen.se/Sighting/137070063</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>137070063</v>
+        <v>137070066</v>
       </c>
       <c r="B142" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16968,13 +16968,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>401559</v>
+        <v>401569</v>
       </c>
       <c r="R142" t="n">
-        <v>6818052</v>
+        <v>6818055</v>
       </c>
       <c r="S142" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17049,16 +17049,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070063</t>
+          <t>https://artportalen.se/Sighting/137070066</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>137070066</v>
+        <v>137071200</v>
       </c>
       <c r="B143" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17090,13 +17090,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>401569</v>
+        <v>401655</v>
       </c>
       <c r="R143" t="n">
-        <v>6818055</v>
+        <v>6818169</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17149,38 +17149,38 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070066</t>
+          <t>https://artportalen.se/Sighting/137071200</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>137071200</v>
+        <v>131046731</v>
       </c>
       <c r="B144" t="n">
-        <v>79274</v>
+        <v>79917</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17188,21 +17188,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -17212,13 +17212,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>401655</v>
+        <v>401560</v>
       </c>
       <c r="R144" t="n">
-        <v>6818169</v>
+        <v>6817813</v>
       </c>
       <c r="S144" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -17242,22 +17242,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17268,41 +17268,31 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137071200</t>
+          <t>https://artportalen.se/Sighting/131046731</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131046731</v>
+        <v>137070052</v>
       </c>
       <c r="B145" t="n">
-        <v>79917</v>
+        <v>80111</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17334,13 +17324,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>401560</v>
+        <v>401393</v>
       </c>
       <c r="R145" t="n">
-        <v>6817813</v>
+        <v>6818202</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17364,22 +17354,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17390,31 +17380,41 @@
       </c>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Elisa Andersson, Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131046731</t>
+          <t>https://artportalen.se/Sighting/137070052</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>137070052</v>
+        <v>137071212</v>
       </c>
       <c r="B146" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17446,13 +17446,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>401393</v>
+        <v>401469</v>
       </c>
       <c r="R146" t="n">
-        <v>6818202</v>
+        <v>6818315</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17505,38 +17505,38 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137070052</t>
+          <t>https://artportalen.se/Sighting/137071212</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>137071212</v>
+        <v>137071254</v>
       </c>
       <c r="B147" t="n">
-        <v>80106</v>
+        <v>79544</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17544,21 +17544,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>401469</v>
+        <v>401576</v>
       </c>
       <c r="R147" t="n">
-        <v>6818315</v>
+        <v>6818045</v>
       </c>
       <c r="S147" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17624,16 +17624,6 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -17648,118 +17638,6 @@
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137071212</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>137071254</v>
-      </c>
-      <c r="B148" t="n">
-        <v>79539</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Blomkällan, Dlr</t>
-        </is>
-      </c>
-      <c r="Q148" t="n">
-        <v>401576</v>
-      </c>
-      <c r="R148" t="n">
-        <v>6818045</v>
-      </c>
-      <c r="S148" t="n">
-        <v>5</v>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AD148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT148" t="inlineStr"/>
-      <c r="AW148" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist</t>
-        </is>
-      </c>
-      <c r="AX148" t="inlineStr">
-        <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
-      <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137071254</t>
         </is>
@@ -17913,7 +17791,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -4035,7 +4035,7 @@
         <v>401434</v>
       </c>
       <c r="R31" t="n">
-        <v>6818304</v>
+        <v>6818305</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -16468,7 +16468,7 @@
         <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071244</v>
       </c>
       <c r="B12" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071289</v>
       </c>
       <c r="B13" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137070046</v>
       </c>
       <c r="B14" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>137071221</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137071222</v>
       </c>
       <c r="B16" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137070028</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070030</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070036</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070038</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070058</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070061</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070068</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070069</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>137070070</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>137070073</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070076</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137071204</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>137071205</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>137071209</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>137071218</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137071229</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>137071247</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>137071253</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>137071257</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>137071258</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>137071259</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137071262</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137071265</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>137071267</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137071271</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137071272</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>137071275</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>137071278</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>137071279</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>137071281</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>137071282</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>137071286</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>137071288</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>137071290</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>137071291</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>137071293</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>137071294</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>137071220</v>
       </c>
       <c r="B68" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071232</v>
       </c>
       <c r="B69" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071234</v>
       </c>
       <c r="B70" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>137071210</v>
       </c>
       <c r="B73" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>137070048</v>
       </c>
       <c r="B74" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070059</v>
       </c>
       <c r="B75" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070064</v>
       </c>
       <c r="B76" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137071239</v>
       </c>
       <c r="B77" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071249</v>
       </c>
       <c r="B78" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071251</v>
       </c>
       <c r="B79" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137070047</v>
       </c>
       <c r="B80" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070049</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070050</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070051</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070054</v>
       </c>
       <c r="B84" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070056</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070060</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070065</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137071213</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071219</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137071224</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>137071225</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>137071230</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137071231</v>
       </c>
       <c r="B93" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>137071250</v>
       </c>
       <c r="B94" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071252</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071256</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>137071264</v>
       </c>
       <c r="B97" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071266</v>
       </c>
       <c r="B98" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071268</v>
       </c>
       <c r="B99" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>137071261</v>
       </c>
       <c r="B101" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>137071287</v>
       </c>
       <c r="B137" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>137070057</v>
       </c>
       <c r="B140" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070063</v>
       </c>
       <c r="B141" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070066</v>
       </c>
       <c r="B142" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137071200</v>
       </c>
       <c r="B143" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137070052</v>
       </c>
       <c r="B145" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137071212</v>
       </c>
       <c r="B146" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071254</v>
       </c>
       <c r="B147" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071244</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071289</v>
       </c>
       <c r="B13" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137070046</v>
       </c>
       <c r="B14" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>137071221</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137071222</v>
       </c>
       <c r="B16" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137070028</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070030</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070036</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070038</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070058</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070061</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070068</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070069</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>137070070</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>137070073</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070076</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137071204</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>137071205</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>137071209</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>137071218</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137071229</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>137071247</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>137071253</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>137071257</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>137071258</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>137071259</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137071262</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137071265</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>137071267</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137071271</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137071272</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>137071275</v>
       </c>
       <c r="B55" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>137071278</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>137071279</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>137071281</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>137071282</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>137071286</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>137071288</v>
       </c>
       <c r="B61" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>137071290</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>137071291</v>
       </c>
       <c r="B63" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>137071293</v>
       </c>
       <c r="B64" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>137071294</v>
       </c>
       <c r="B65" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>137071220</v>
       </c>
       <c r="B68" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071232</v>
       </c>
       <c r="B69" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071234</v>
       </c>
       <c r="B70" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>137071210</v>
       </c>
       <c r="B73" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>137070048</v>
       </c>
       <c r="B74" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070059</v>
       </c>
       <c r="B75" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070064</v>
       </c>
       <c r="B76" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137071239</v>
       </c>
       <c r="B77" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071249</v>
       </c>
       <c r="B78" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071251</v>
       </c>
       <c r="B79" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137070047</v>
       </c>
       <c r="B80" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070049</v>
       </c>
       <c r="B81" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070050</v>
       </c>
       <c r="B82" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070051</v>
       </c>
       <c r="B83" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070054</v>
       </c>
       <c r="B84" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070056</v>
       </c>
       <c r="B85" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070060</v>
       </c>
       <c r="B86" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070065</v>
       </c>
       <c r="B87" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137071213</v>
       </c>
       <c r="B88" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071219</v>
       </c>
       <c r="B89" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137071224</v>
       </c>
       <c r="B90" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>137071225</v>
       </c>
       <c r="B91" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>137071230</v>
       </c>
       <c r="B92" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137071231</v>
       </c>
       <c r="B93" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>137071250</v>
       </c>
       <c r="B94" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071252</v>
       </c>
       <c r="B95" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071256</v>
       </c>
       <c r="B96" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>137071264</v>
       </c>
       <c r="B97" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071266</v>
       </c>
       <c r="B98" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071268</v>
       </c>
       <c r="B99" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>137071261</v>
       </c>
       <c r="B101" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>137071287</v>
       </c>
       <c r="B137" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>137070057</v>
       </c>
       <c r="B140" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070063</v>
       </c>
       <c r="B141" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070066</v>
       </c>
       <c r="B142" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137071200</v>
       </c>
       <c r="B143" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137070052</v>
       </c>
       <c r="B145" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137071212</v>
       </c>
       <c r="B146" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071254</v>
       </c>
       <c r="B147" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071244</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071289</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137070046</v>
       </c>
       <c r="B14" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>137071221</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137071222</v>
       </c>
       <c r="B16" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137070028</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070030</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070036</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>401434</v>
       </c>
       <c r="R31" t="n">
-        <v>6818305</v>
+        <v>6818304</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4122,7 +4122,7 @@
         <v>137070038</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070058</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070061</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070068</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070069</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>137070070</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>137070073</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070076</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137071204</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>137071205</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>137071209</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>137071218</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137071229</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>137071247</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>137071253</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>137071257</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>137071258</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>137071259</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137071262</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137071265</v>
       </c>
       <c r="B51" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>137071267</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137071271</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137071272</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>137071275</v>
       </c>
       <c r="B55" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>137071278</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>137071279</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>137071281</v>
       </c>
       <c r="B58" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>137071282</v>
       </c>
       <c r="B59" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>137071286</v>
       </c>
       <c r="B60" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>137071288</v>
       </c>
       <c r="B61" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>137071290</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>137071291</v>
       </c>
       <c r="B63" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>137071293</v>
       </c>
       <c r="B64" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>137071294</v>
       </c>
       <c r="B65" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>137071220</v>
       </c>
       <c r="B68" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071232</v>
       </c>
       <c r="B69" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071234</v>
       </c>
       <c r="B70" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>137071210</v>
       </c>
       <c r="B73" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>137070048</v>
       </c>
       <c r="B74" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070059</v>
       </c>
       <c r="B75" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070064</v>
       </c>
       <c r="B76" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137071239</v>
       </c>
       <c r="B77" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071249</v>
       </c>
       <c r="B78" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071251</v>
       </c>
       <c r="B79" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137070047</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070049</v>
       </c>
       <c r="B81" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070050</v>
       </c>
       <c r="B82" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070051</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070054</v>
       </c>
       <c r="B84" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070056</v>
       </c>
       <c r="B85" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070060</v>
       </c>
       <c r="B86" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070065</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137071213</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071219</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137071224</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>137071225</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>137071230</v>
       </c>
       <c r="B92" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137071231</v>
       </c>
       <c r="B93" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>137071250</v>
       </c>
       <c r="B94" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071252</v>
       </c>
       <c r="B95" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071256</v>
       </c>
       <c r="B96" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>137071264</v>
       </c>
       <c r="B97" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071266</v>
       </c>
       <c r="B98" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071268</v>
       </c>
       <c r="B99" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>137071261</v>
       </c>
       <c r="B101" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>137071287</v>
       </c>
       <c r="B137" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>137070057</v>
       </c>
       <c r="B140" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070063</v>
       </c>
       <c r="B141" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070066</v>
       </c>
       <c r="B142" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137071200</v>
       </c>
       <c r="B143" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137070052</v>
       </c>
       <c r="B145" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137071212</v>
       </c>
       <c r="B146" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071254</v>
       </c>
       <c r="B147" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -4035,7 +4035,7 @@
         <v>401434</v>
       </c>
       <c r="R31" t="n">
-        <v>6818304</v>
+        <v>6818305</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 59303-2025 artfynd.xlsx
+++ b/artfynd/A 59303-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137070055</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137071206</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137071227</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>137071246</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137071260</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>137071269</v>
       </c>
       <c r="B8" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>137071274</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>137071283</v>
       </c>
       <c r="B10" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137071226</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>137071244</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>137071289</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>137070046</v>
       </c>
       <c r="B14" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>137071221</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137071222</v>
       </c>
       <c r="B16" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137070028</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>137070030</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>137070036</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>137070038</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>137070058</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>137070061</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>137070068</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>137070069</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>137070070</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>137070073</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>137070076</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>137071204</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>137071205</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>137071209</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>137071218</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>137071229</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>137071247</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>137071253</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>137071257</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>137071258</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>137071259</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>137071262</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>137071265</v>
       </c>
       <c r="B51" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>137071267</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137071271</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137071272</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>137071275</v>
       </c>
       <c r="B55" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>137071278</v>
       </c>
       <c r="B56" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>137071279</v>
       </c>
       <c r="B57" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>137071281</v>
       </c>
       <c r="B58" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>137071282</v>
       </c>
       <c r="B59" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>137071286</v>
       </c>
       <c r="B60" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>137071288</v>
       </c>
       <c r="B61" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>137071290</v>
       </c>
       <c r="B62" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>137071291</v>
       </c>
       <c r="B63" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>137071293</v>
       </c>
       <c r="B64" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>137071294</v>
       </c>
       <c r="B65" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>137071220</v>
       </c>
       <c r="B68" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137071232</v>
       </c>
       <c r="B69" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>137071234</v>
       </c>
       <c r="B70" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>137071210</v>
       </c>
       <c r="B73" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>137070048</v>
       </c>
       <c r="B74" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>137070059</v>
       </c>
       <c r="B75" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>137070064</v>
       </c>
       <c r="B76" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137071239</v>
       </c>
       <c r="B77" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>137071249</v>
       </c>
       <c r="B78" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137071251</v>
       </c>
       <c r="B79" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>137070047</v>
       </c>
       <c r="B80" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>137070049</v>
       </c>
       <c r="B81" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>137070050</v>
       </c>
       <c r="B82" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>137070051</v>
       </c>
       <c r="B83" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>137070054</v>
       </c>
       <c r="B84" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>137070056</v>
       </c>
       <c r="B85" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>137070060</v>
       </c>
       <c r="B86" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>137070065</v>
       </c>
       <c r="B87" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>137071213</v>
       </c>
       <c r="B88" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>137071219</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>137071224</v>
       </c>
       <c r="B90" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>137071225</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>137071230</v>
       </c>
       <c r="B92" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137071231</v>
       </c>
       <c r="B93" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>137071250</v>
       </c>
       <c r="B94" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>137071252</v>
       </c>
       <c r="B95" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>137071256</v>
       </c>
       <c r="B96" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>137071264</v>
       </c>
       <c r="B97" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>137071266</v>
       </c>
       <c r="B98" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>137071268</v>
       </c>
       <c r="B99" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>137071261</v>
       </c>
       <c r="B101" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>137071277</v>
       </c>
       <c r="B102" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137071199</v>
       </c>
       <c r="B103" t="n">
-        <v>58149</v>
+        <v>58152</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137070033</v>
       </c>
       <c r="B114" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>137070039</v>
       </c>
       <c r="B115" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>137070044</v>
       </c>
       <c r="B116" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>137070062</v>
       </c>
       <c r="B117" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>137070071</v>
       </c>
       <c r="B118" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>137070075</v>
       </c>
       <c r="B119" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>137071228</v>
       </c>
       <c r="B120" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>137071236</v>
       </c>
       <c r="B121" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>137071237</v>
       </c>
       <c r="B122" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>137071241</v>
       </c>
       <c r="B123" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>137071245</v>
       </c>
       <c r="B124" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>137071248</v>
       </c>
       <c r="B125" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>137071255</v>
       </c>
       <c r="B126" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>137071280</v>
       </c>
       <c r="B127" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>137071284</v>
       </c>
       <c r="B128" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>137071295</v>
       </c>
       <c r="B129" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>137070041</v>
       </c>
       <c r="B130" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>137071201</v>
       </c>
       <c r="B131" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>137071235</v>
       </c>
       <c r="B132" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>137071240</v>
       </c>
       <c r="B135" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>137071276</v>
       </c>
       <c r="B136" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>137071287</v>
       </c>
       <c r="B137" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>137071263</v>
       </c>
       <c r="B138" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>137070057</v>
       </c>
       <c r="B140" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>137070063</v>
       </c>
       <c r="B141" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>137070066</v>
       </c>
       <c r="B142" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>137071200</v>
       </c>
       <c r="B143" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137070052</v>
       </c>
       <c r="B145" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>137071212</v>
       </c>
       <c r="B146" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>137071254</v>
       </c>
       <c r="B147" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
